--- a/artfynd/A 19410-2023 artfynd.xlsx
+++ b/artfynd/A 19410-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ9"/>
+  <dimension ref="A1:AZ11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -793,45 +793,49 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130836029</v>
+        <v>136935836</v>
       </c>
       <c r="B3" t="n">
-        <v>97231</v>
+        <v>99353</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2869</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Girg.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Kysveden, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>519529</v>
+        <v>519304</v>
       </c>
       <c r="R3" t="n">
-        <v>6672236</v>
+        <v>6672233</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -858,12 +862,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-10-14</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-10-14</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -878,27 +882,27 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Tore Dahlberg</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Tore Dahlberg</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130836029</t>
+          <t>https://artportalen.se/Sighting/136935836</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>134324692</v>
+        <v>130836029</v>
       </c>
       <c r="B4" t="n">
-        <v>57165</v>
+        <v>97231</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -906,42 +910,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102613</v>
+        <v>2869</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Siksberget, Dlr</t>
+          <t>Kysveden, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>519402</v>
+        <v>519529</v>
       </c>
       <c r="R4" t="n">
-        <v>6672160</v>
+        <v>6672236</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -968,12 +964,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2025-10-14</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2025-10-14</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -993,19 +989,19 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Elias Blad, Mårten Wikström</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134324692</t>
+          <t>https://artportalen.se/Sighting/130836029</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>134326023</v>
+        <v>134324692</v>
       </c>
       <c r="B5" t="n">
         <v>57165</v>
@@ -1033,31 +1029,25 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Siksberget, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>519460</v>
+        <v>519402</v>
       </c>
       <c r="R5" t="n">
-        <v>6672328</v>
+        <v>6672160</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1084,12 +1074,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1109,22 +1099,22 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Elias Blad, Mårten Wikström</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134326023</t>
+          <t>https://artportalen.se/Sighting/134324692</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>134326032</v>
+        <v>134326023</v>
       </c>
       <c r="B6" t="n">
-        <v>58131</v>
+        <v>57165</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1132,16 +1122,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103023</v>
+        <v>102613</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tofsmes</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lophophanes cristatus</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1154,23 +1144,26 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M6" t="inlineStr">
         <is>
           <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Siksberget, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>519559</v>
+        <v>519460</v>
       </c>
       <c r="R6" t="n">
-        <v>6672326</v>
+        <v>6672328</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1197,12 +1190,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1222,61 +1215,68 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Mårten Wikström</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134326032</t>
+          <t>https://artportalen.se/Sighting/134326023</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130836030</v>
+        <v>134326032</v>
       </c>
       <c r="B7" t="n">
-        <v>99118</v>
+        <v>58131</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>103023</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tofsmes</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lophophanes cristatus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>15</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Kysveden, Dlr</t>
+          <t>Siksberget, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>519550</v>
+        <v>519559</v>
       </c>
       <c r="R7" t="n">
-        <v>6672328</v>
+        <v>6672326</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1303,12 +1303,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-10-14</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-10-14</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1328,19 +1328,19 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Mårten Wikström</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130836030</t>
+          <t>https://artportalen.se/Sighting/134326032</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131007343</v>
+        <v>130836030</v>
       </c>
       <c r="B8" t="n">
         <v>99118</v>
@@ -1368,17 +1368,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Kysveden, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>519522</v>
+        <v>519550</v>
       </c>
       <c r="R8" t="n">
-        <v>6672233</v>
+        <v>6672328</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1425,49 +1429,49 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Sara Lundkvist</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Sara Lundkvist</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131007343</t>
+          <t>https://artportalen.se/Sighting/130836030</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131007342</v>
+        <v>131007343</v>
       </c>
       <c r="B9" t="n">
-        <v>97983</v>
+        <v>99118</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1477,10 +1481,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>519536</v>
+        <v>519522</v>
       </c>
       <c r="R9" t="n">
-        <v>6672276</v>
+        <v>6672233</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1537,6 +1541,214 @@
       </c>
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131007343</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>136935837</v>
+      </c>
+      <c r="B10" t="n">
+        <v>99353</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Kysveden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>519371</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6672256</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Norrbärke</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Tore Dahlberg</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Tore Dahlberg</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136935837</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>131007342</v>
+      </c>
+      <c r="B11" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Kysveden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>519536</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6672276</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Norrbärke</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-10-14</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-10-14</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Sara Lundkvist</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Sara Lundkvist</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/131007342</t>
         </is>
@@ -1552,6 +1764,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 19410-2023 artfynd.xlsx
+++ b/artfynd/A 19410-2023 artfynd.xlsx
@@ -796,7 +796,7 @@
         <v>136935836</v>
       </c>
       <c r="B3" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>136935837</v>
       </c>
       <c r="B10" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 19410-2023 artfynd.xlsx
+++ b/artfynd/A 19410-2023 artfynd.xlsx
@@ -796,7 +796,7 @@
         <v>136935836</v>
       </c>
       <c r="B3" t="n">
-        <v>99359</v>
+        <v>99361</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>136935837</v>
       </c>
       <c r="B10" t="n">
-        <v>99359</v>
+        <v>99361</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 19410-2023 artfynd.xlsx
+++ b/artfynd/A 19410-2023 artfynd.xlsx
@@ -796,7 +796,7 @@
         <v>136935836</v>
       </c>
       <c r="B3" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>136935837</v>
       </c>
       <c r="B10" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 19410-2023 artfynd.xlsx
+++ b/artfynd/A 19410-2023 artfynd.xlsx
@@ -796,7 +796,7 @@
         <v>136935836</v>
       </c>
       <c r="B3" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>136935837</v>
       </c>
       <c r="B10" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 19410-2023 artfynd.xlsx
+++ b/artfynd/A 19410-2023 artfynd.xlsx
@@ -796,7 +796,7 @@
         <v>136935836</v>
       </c>
       <c r="B3" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>136935837</v>
       </c>
       <c r="B10" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 19410-2023 artfynd.xlsx
+++ b/artfynd/A 19410-2023 artfynd.xlsx
@@ -796,7 +796,7 @@
         <v>136935836</v>
       </c>
       <c r="B3" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>136935837</v>
       </c>
       <c r="B10" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 19410-2023 artfynd.xlsx
+++ b/artfynd/A 19410-2023 artfynd.xlsx
@@ -796,7 +796,7 @@
         <v>136935836</v>
       </c>
       <c r="B3" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>136935837</v>
       </c>
       <c r="B10" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 19410-2023 artfynd.xlsx
+++ b/artfynd/A 19410-2023 artfynd.xlsx
@@ -796,7 +796,7 @@
         <v>136935836</v>
       </c>
       <c r="B3" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>136935837</v>
       </c>
       <c r="B10" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 19410-2023 artfynd.xlsx
+++ b/artfynd/A 19410-2023 artfynd.xlsx
@@ -796,7 +796,7 @@
         <v>136935836</v>
       </c>
       <c r="B3" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>136935837</v>
       </c>
       <c r="B10" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 19410-2023 artfynd.xlsx
+++ b/artfynd/A 19410-2023 artfynd.xlsx
@@ -796,7 +796,7 @@
         <v>136935836</v>
       </c>
       <c r="B3" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>136935837</v>
       </c>
       <c r="B10" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 19410-2023 artfynd.xlsx
+++ b/artfynd/A 19410-2023 artfynd.xlsx
@@ -796,7 +796,7 @@
         <v>136935836</v>
       </c>
       <c r="B3" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>136935837</v>
       </c>
       <c r="B10" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 19410-2023 artfynd.xlsx
+++ b/artfynd/A 19410-2023 artfynd.xlsx
@@ -796,7 +796,7 @@
         <v>136935836</v>
       </c>
       <c r="B3" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>136935837</v>
       </c>
       <c r="B10" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 19410-2023 artfynd.xlsx
+++ b/artfynd/A 19410-2023 artfynd.xlsx
@@ -796,7 +796,7 @@
         <v>136935836</v>
       </c>
       <c r="B3" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>136935837</v>
       </c>
       <c r="B10" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 19410-2023 artfynd.xlsx
+++ b/artfynd/A 19410-2023 artfynd.xlsx
@@ -796,7 +796,7 @@
         <v>136935836</v>
       </c>
       <c r="B3" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>136935837</v>
       </c>
       <c r="B10" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 19410-2023 artfynd.xlsx
+++ b/artfynd/A 19410-2023 artfynd.xlsx
@@ -796,7 +796,7 @@
         <v>136935836</v>
       </c>
       <c r="B3" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>136935837</v>
       </c>
       <c r="B10" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 19410-2023 artfynd.xlsx
+++ b/artfynd/A 19410-2023 artfynd.xlsx
@@ -796,7 +796,7 @@
         <v>136935836</v>
       </c>
       <c r="B3" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>136935837</v>
       </c>
       <c r="B10" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 19410-2023 artfynd.xlsx
+++ b/artfynd/A 19410-2023 artfynd.xlsx
@@ -796,7 +796,7 @@
         <v>136935836</v>
       </c>
       <c r="B3" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>136935837</v>
       </c>
       <c r="B10" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 19410-2023 artfynd.xlsx
+++ b/artfynd/A 19410-2023 artfynd.xlsx
@@ -796,7 +796,7 @@
         <v>136935836</v>
       </c>
       <c r="B3" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>136935837</v>
       </c>
       <c r="B10" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 19410-2023 artfynd.xlsx
+++ b/artfynd/A 19410-2023 artfynd.xlsx
@@ -796,7 +796,7 @@
         <v>136935836</v>
       </c>
       <c r="B3" t="n">
-        <v>99434</v>
+        <v>99435</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>136935837</v>
       </c>
       <c r="B10" t="n">
-        <v>99434</v>
+        <v>99435</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 19410-2023 artfynd.xlsx
+++ b/artfynd/A 19410-2023 artfynd.xlsx
@@ -796,7 +796,7 @@
         <v>136935836</v>
       </c>
       <c r="B3" t="n">
-        <v>99435</v>
+        <v>99438</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>136935837</v>
       </c>
       <c r="B10" t="n">
-        <v>99435</v>
+        <v>99438</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
